--- a/Sep_2026/Daily Sale/New Fomat.xlsx
+++ b/Sep_2026/Daily Sale/New Fomat.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9FC79F3-C843-4BAC-B15F-746C24FDB39A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6285BA2-A23A-41A4-9760-DC9CD625A43F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="948" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3948" uniqueCount="514">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3948" uniqueCount="515">
   <si>
     <t>Sr.No</t>
   </si>
@@ -1597,6 +1597,9 @@
   </si>
   <si>
     <t xml:space="preserve">Address: Adress </t>
+  </si>
+  <si>
+    <t>Jabbar</t>
   </si>
 </sst>
 </file>
@@ -3872,6 +3875,71 @@
     </dxf>
     <dxf>
       <font>
+        <b/>
+        <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="10"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="10"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="10"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="10"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="10"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -4293,71 +4361,6 @@
         <color indexed="10"/>
       </font>
     </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
   <extLst>
@@ -7146,8 +7149,8 @@
       <c r="L4" s="370"/>
       <c r="M4" s="370"/>
       <c r="N4" s="400">
-        <f ca="1">'1'!N4:P4</f>
-        <v>46266</v>
+        <f ca="1">'1'!N4:P5</f>
+        <v>46269</v>
       </c>
       <c r="O4" s="400"/>
       <c r="P4" s="400"/>
@@ -7175,7 +7178,7 @@
       <c r="M5" s="370"/>
       <c r="N5" s="400">
         <f ca="1">N4-1</f>
-        <v>46265</v>
+        <v>46268</v>
       </c>
       <c r="O5" s="369"/>
       <c r="P5" s="369"/>
@@ -7197,7 +7200,7 @@
       <c r="M6" s="370"/>
       <c r="N6" s="399" t="str">
         <f>Summary!H2</f>
-        <v>Booker Name</v>
+        <v>Jabbar</v>
       </c>
       <c r="O6" s="399"/>
       <c r="P6" s="399"/>
@@ -8571,7 +8574,7 @@
       <c r="M4" s="370"/>
       <c r="N4" s="400">
         <f ca="1">'1'!N4:P4</f>
-        <v>46266</v>
+        <v>46269</v>
       </c>
       <c r="O4" s="400"/>
       <c r="P4" s="400"/>
@@ -8599,7 +8602,7 @@
       <c r="M5" s="370"/>
       <c r="N5" s="400">
         <f ca="1">N4-1</f>
-        <v>46265</v>
+        <v>46268</v>
       </c>
       <c r="O5" s="369"/>
       <c r="P5" s="369"/>
@@ -8621,7 +8624,7 @@
       <c r="M6" s="370"/>
       <c r="N6" s="399" t="str">
         <f>Summary!H2</f>
-        <v>Booker Name</v>
+        <v>Jabbar</v>
       </c>
       <c r="O6" s="399"/>
       <c r="P6" s="399"/>
@@ -9995,7 +9998,7 @@
       <c r="M4" s="370"/>
       <c r="N4" s="400">
         <f ca="1">'1'!N4:P4</f>
-        <v>46266</v>
+        <v>46269</v>
       </c>
       <c r="O4" s="400"/>
       <c r="P4" s="400"/>
@@ -10023,7 +10026,7 @@
       <c r="M5" s="370"/>
       <c r="N5" s="400">
         <f ca="1">N4-1</f>
-        <v>46265</v>
+        <v>46268</v>
       </c>
       <c r="O5" s="369"/>
       <c r="P5" s="369"/>
@@ -10045,7 +10048,7 @@
       <c r="M6" s="370"/>
       <c r="N6" s="399" t="str">
         <f>Summary!H2</f>
-        <v>Booker Name</v>
+        <v>Jabbar</v>
       </c>
       <c r="O6" s="399"/>
       <c r="P6" s="399"/>
@@ -11419,7 +11422,7 @@
       <c r="M4" s="370"/>
       <c r="N4" s="400">
         <f ca="1">'1'!N4:P4</f>
-        <v>46266</v>
+        <v>46269</v>
       </c>
       <c r="O4" s="400"/>
       <c r="P4" s="400"/>
@@ -11447,7 +11450,7 @@
       <c r="M5" s="370"/>
       <c r="N5" s="400">
         <f ca="1">N4-1</f>
-        <v>46265</v>
+        <v>46268</v>
       </c>
       <c r="O5" s="369"/>
       <c r="P5" s="369"/>
@@ -11469,7 +11472,7 @@
       <c r="M6" s="370"/>
       <c r="N6" s="399" t="str">
         <f>Summary!H2</f>
-        <v>Booker Name</v>
+        <v>Jabbar</v>
       </c>
       <c r="O6" s="399"/>
       <c r="P6" s="399"/>
@@ -12843,7 +12846,7 @@
       <c r="M4" s="370"/>
       <c r="N4" s="400">
         <f ca="1">'1'!N4:P4</f>
-        <v>46266</v>
+        <v>46269</v>
       </c>
       <c r="O4" s="400"/>
       <c r="P4" s="400"/>
@@ -12871,7 +12874,7 @@
       <c r="M5" s="370"/>
       <c r="N5" s="400">
         <f ca="1">N4-1</f>
-        <v>46265</v>
+        <v>46268</v>
       </c>
       <c r="O5" s="369"/>
       <c r="P5" s="369"/>
@@ -12893,7 +12896,7 @@
       <c r="M6" s="370"/>
       <c r="N6" s="399" t="str">
         <f>Summary!H2</f>
-        <v>Booker Name</v>
+        <v>Jabbar</v>
       </c>
       <c r="O6" s="399"/>
       <c r="P6" s="399"/>
@@ -14267,7 +14270,7 @@
       <c r="M4" s="370"/>
       <c r="N4" s="400">
         <f ca="1">'1'!N4:P4</f>
-        <v>46266</v>
+        <v>46269</v>
       </c>
       <c r="O4" s="400"/>
       <c r="P4" s="400"/>
@@ -14295,7 +14298,7 @@
       <c r="M5" s="370"/>
       <c r="N5" s="400">
         <f ca="1">N4-1</f>
-        <v>46265</v>
+        <v>46268</v>
       </c>
       <c r="O5" s="369"/>
       <c r="P5" s="369"/>
@@ -14317,7 +14320,7 @@
       <c r="M6" s="370"/>
       <c r="N6" s="399" t="str">
         <f>Summary!H2</f>
-        <v>Booker Name</v>
+        <v>Jabbar</v>
       </c>
       <c r="O6" s="399"/>
       <c r="P6" s="399"/>
@@ -15691,7 +15694,7 @@
       <c r="M4" s="370"/>
       <c r="N4" s="400">
         <f ca="1">'1'!N4:P4</f>
-        <v>46266</v>
+        <v>46269</v>
       </c>
       <c r="O4" s="400"/>
       <c r="P4" s="400"/>
@@ -15719,7 +15722,7 @@
       <c r="M5" s="370"/>
       <c r="N5" s="400">
         <f ca="1">N4-1</f>
-        <v>46265</v>
+        <v>46268</v>
       </c>
       <c r="O5" s="369"/>
       <c r="P5" s="369"/>
@@ -15741,7 +15744,7 @@
       <c r="M6" s="370"/>
       <c r="N6" s="399" t="str">
         <f>Summary!H2</f>
-        <v>Booker Name</v>
+        <v>Jabbar</v>
       </c>
       <c r="O6" s="399"/>
       <c r="P6" s="399"/>
@@ -17115,7 +17118,7 @@
       <c r="M4" s="370"/>
       <c r="N4" s="400">
         <f ca="1">'1'!N4:P4</f>
-        <v>46266</v>
+        <v>46269</v>
       </c>
       <c r="O4" s="400"/>
       <c r="P4" s="400"/>
@@ -17143,7 +17146,7 @@
       <c r="M5" s="370"/>
       <c r="N5" s="400">
         <f ca="1">N4-1</f>
-        <v>46265</v>
+        <v>46268</v>
       </c>
       <c r="O5" s="369"/>
       <c r="P5" s="369"/>
@@ -17165,7 +17168,7 @@
       <c r="M6" s="370"/>
       <c r="N6" s="399" t="str">
         <f>Summary!H2</f>
-        <v>Booker Name</v>
+        <v>Jabbar</v>
       </c>
       <c r="O6" s="399"/>
       <c r="P6" s="399"/>
@@ -18539,7 +18542,7 @@
       <c r="M4" s="370"/>
       <c r="N4" s="400">
         <f ca="1">'1'!N4:P4</f>
-        <v>46266</v>
+        <v>46269</v>
       </c>
       <c r="O4" s="400"/>
       <c r="P4" s="400"/>
@@ -18567,7 +18570,7 @@
       <c r="M5" s="370"/>
       <c r="N5" s="400">
         <f ca="1">N4-1</f>
-        <v>46265</v>
+        <v>46268</v>
       </c>
       <c r="O5" s="369"/>
       <c r="P5" s="369"/>
@@ -18589,7 +18592,7 @@
       <c r="M6" s="370"/>
       <c r="N6" s="399" t="str">
         <f>Summary!H2</f>
-        <v>Booker Name</v>
+        <v>Jabbar</v>
       </c>
       <c r="O6" s="399"/>
       <c r="P6" s="399"/>
@@ -19963,7 +19966,7 @@
       <c r="M4" s="370"/>
       <c r="N4" s="400">
         <f ca="1">'1'!N4:P4</f>
-        <v>46266</v>
+        <v>46269</v>
       </c>
       <c r="O4" s="400"/>
       <c r="P4" s="400"/>
@@ -19991,7 +19994,7 @@
       <c r="M5" s="370"/>
       <c r="N5" s="400">
         <f ca="1">N4-1</f>
-        <v>46265</v>
+        <v>46268</v>
       </c>
       <c r="O5" s="369"/>
       <c r="P5" s="369"/>
@@ -20013,7 +20016,7 @@
       <c r="M6" s="370"/>
       <c r="N6" s="399" t="str">
         <f>Summary!H2</f>
-        <v>Booker Name</v>
+        <v>Jabbar</v>
       </c>
       <c r="O6" s="399"/>
       <c r="P6" s="399"/>
@@ -23802,7 +23805,7 @@
       <c r="M4" s="370"/>
       <c r="N4" s="400">
         <f ca="1">'1'!N4:P4</f>
-        <v>46266</v>
+        <v>46269</v>
       </c>
       <c r="O4" s="400"/>
       <c r="P4" s="400"/>
@@ -23830,7 +23833,7 @@
       <c r="M5" s="370"/>
       <c r="N5" s="400">
         <f ca="1">N4-1</f>
-        <v>46265</v>
+        <v>46268</v>
       </c>
       <c r="O5" s="369"/>
       <c r="P5" s="369"/>
@@ -23852,7 +23855,7 @@
       <c r="M6" s="370"/>
       <c r="N6" s="399" t="str">
         <f>Summary!H2</f>
-        <v>Booker Name</v>
+        <v>Jabbar</v>
       </c>
       <c r="O6" s="399"/>
       <c r="P6" s="399"/>
@@ -25226,7 +25229,7 @@
       <c r="M4" s="370"/>
       <c r="N4" s="400">
         <f ca="1">'1'!N4:P4</f>
-        <v>46266</v>
+        <v>46269</v>
       </c>
       <c r="O4" s="400"/>
       <c r="P4" s="400"/>
@@ -25254,7 +25257,7 @@
       <c r="M5" s="370"/>
       <c r="N5" s="400">
         <f ca="1">N4-1</f>
-        <v>46265</v>
+        <v>46268</v>
       </c>
       <c r="O5" s="369"/>
       <c r="P5" s="369"/>
@@ -25276,7 +25279,7 @@
       <c r="M6" s="370"/>
       <c r="N6" s="399" t="str">
         <f>Summary!H2</f>
-        <v>Booker Name</v>
+        <v>Jabbar</v>
       </c>
       <c r="O6" s="399"/>
       <c r="P6" s="399"/>
@@ -26650,7 +26653,7 @@
       <c r="M4" s="370"/>
       <c r="N4" s="400">
         <f ca="1">'1'!N4:P4</f>
-        <v>46266</v>
+        <v>46269</v>
       </c>
       <c r="O4" s="400"/>
       <c r="P4" s="400"/>
@@ -26678,7 +26681,7 @@
       <c r="M5" s="370"/>
       <c r="N5" s="400">
         <f ca="1">N4-1</f>
-        <v>46265</v>
+        <v>46268</v>
       </c>
       <c r="O5" s="369"/>
       <c r="P5" s="369"/>
@@ -26700,7 +26703,7 @@
       <c r="M6" s="370"/>
       <c r="N6" s="399" t="str">
         <f>Summary!H2</f>
-        <v>Booker Name</v>
+        <v>Jabbar</v>
       </c>
       <c r="O6" s="399"/>
       <c r="P6" s="399"/>
@@ -28074,7 +28077,7 @@
       <c r="M4" s="370"/>
       <c r="N4" s="400">
         <f ca="1">'1'!N4:P4</f>
-        <v>46266</v>
+        <v>46269</v>
       </c>
       <c r="O4" s="400"/>
       <c r="P4" s="400"/>
@@ -28102,7 +28105,7 @@
       <c r="M5" s="370"/>
       <c r="N5" s="400">
         <f ca="1">N4-1</f>
-        <v>46265</v>
+        <v>46268</v>
       </c>
       <c r="O5" s="369"/>
       <c r="P5" s="369"/>
@@ -28124,7 +28127,7 @@
       <c r="M6" s="370"/>
       <c r="N6" s="399" t="str">
         <f>Summary!H2</f>
-        <v>Booker Name</v>
+        <v>Jabbar</v>
       </c>
       <c r="O6" s="399"/>
       <c r="P6" s="399"/>
@@ -29498,7 +29501,7 @@
       <c r="M4" s="370"/>
       <c r="N4" s="400">
         <f ca="1">'1'!N4:P4</f>
-        <v>46266</v>
+        <v>46269</v>
       </c>
       <c r="O4" s="400"/>
       <c r="P4" s="400"/>
@@ -29526,7 +29529,7 @@
       <c r="M5" s="370"/>
       <c r="N5" s="400">
         <f ca="1">N4-1</f>
-        <v>46265</v>
+        <v>46268</v>
       </c>
       <c r="O5" s="369"/>
       <c r="P5" s="369"/>
@@ -29548,7 +29551,7 @@
       <c r="M6" s="370"/>
       <c r="N6" s="399" t="str">
         <f>Summary!H2</f>
-        <v>Booker Name</v>
+        <v>Jabbar</v>
       </c>
       <c r="O6" s="399"/>
       <c r="P6" s="399"/>
@@ -30922,7 +30925,7 @@
       <c r="M4" s="370"/>
       <c r="N4" s="400">
         <f ca="1">'1'!N4:P4</f>
-        <v>46266</v>
+        <v>46269</v>
       </c>
       <c r="O4" s="400"/>
       <c r="P4" s="400"/>
@@ -30950,7 +30953,7 @@
       <c r="M5" s="370"/>
       <c r="N5" s="400">
         <f ca="1">N4-1</f>
-        <v>46265</v>
+        <v>46268</v>
       </c>
       <c r="O5" s="369"/>
       <c r="P5" s="369"/>
@@ -30972,7 +30975,7 @@
       <c r="M6" s="370"/>
       <c r="N6" s="399" t="str">
         <f>Summary!H2</f>
-        <v>Booker Name</v>
+        <v>Jabbar</v>
       </c>
       <c r="O6" s="399"/>
       <c r="P6" s="399"/>
@@ -32346,7 +32349,7 @@
       <c r="M4" s="370"/>
       <c r="N4" s="400">
         <f ca="1">'1'!N4:P4</f>
-        <v>46266</v>
+        <v>46269</v>
       </c>
       <c r="O4" s="400"/>
       <c r="P4" s="400"/>
@@ -32374,7 +32377,7 @@
       <c r="M5" s="370"/>
       <c r="N5" s="400">
         <f ca="1">N4-1</f>
-        <v>46265</v>
+        <v>46268</v>
       </c>
       <c r="O5" s="369"/>
       <c r="P5" s="369"/>
@@ -32396,7 +32399,7 @@
       <c r="M6" s="370"/>
       <c r="N6" s="399" t="str">
         <f>Summary!H2</f>
-        <v>Booker Name</v>
+        <v>Jabbar</v>
       </c>
       <c r="O6" s="399"/>
       <c r="P6" s="399"/>
@@ -33770,7 +33773,7 @@
       <c r="M4" s="370"/>
       <c r="N4" s="400">
         <f ca="1">'1'!N4:P4</f>
-        <v>46266</v>
+        <v>46269</v>
       </c>
       <c r="O4" s="400"/>
       <c r="P4" s="400"/>
@@ -33798,7 +33801,7 @@
       <c r="M5" s="370"/>
       <c r="N5" s="400">
         <f ca="1">N4-1</f>
-        <v>46265</v>
+        <v>46268</v>
       </c>
       <c r="O5" s="369"/>
       <c r="P5" s="369"/>
@@ -33820,7 +33823,7 @@
       <c r="M6" s="370"/>
       <c r="N6" s="399" t="str">
         <f>Summary!H2</f>
-        <v>Booker Name</v>
+        <v>Jabbar</v>
       </c>
       <c r="O6" s="399"/>
       <c r="P6" s="399"/>
@@ -35194,7 +35197,7 @@
       <c r="M4" s="370"/>
       <c r="N4" s="400">
         <f ca="1">'1'!N4:P4</f>
-        <v>46266</v>
+        <v>46269</v>
       </c>
       <c r="O4" s="400"/>
       <c r="P4" s="400"/>
@@ -35222,7 +35225,7 @@
       <c r="M5" s="370"/>
       <c r="N5" s="400">
         <f ca="1">N4-1</f>
-        <v>46265</v>
+        <v>46268</v>
       </c>
       <c r="O5" s="369"/>
       <c r="P5" s="369"/>
@@ -35244,7 +35247,7 @@
       <c r="M6" s="370"/>
       <c r="N6" s="399" t="str">
         <f>Summary!H2</f>
-        <v>Booker Name</v>
+        <v>Jabbar</v>
       </c>
       <c r="O6" s="399"/>
       <c r="P6" s="399"/>
@@ -36618,7 +36621,7 @@
       <c r="M4" s="370"/>
       <c r="N4" s="400">
         <f ca="1">'1'!N4:P4</f>
-        <v>46266</v>
+        <v>46269</v>
       </c>
       <c r="O4" s="400"/>
       <c r="P4" s="400"/>
@@ -36646,7 +36649,7 @@
       <c r="M5" s="370"/>
       <c r="N5" s="400">
         <f ca="1">N4-1</f>
-        <v>46265</v>
+        <v>46268</v>
       </c>
       <c r="O5" s="369"/>
       <c r="P5" s="369"/>
@@ -36668,7 +36671,7 @@
       <c r="M6" s="370"/>
       <c r="N6" s="399" t="str">
         <f>Summary!H2</f>
-        <v>Booker Name</v>
+        <v>Jabbar</v>
       </c>
       <c r="O6" s="399"/>
       <c r="P6" s="399"/>
@@ -40705,35 +40708,35 @@
     <mergeCell ref="X4:Y4"/>
   </mergeCells>
   <conditionalFormatting sqref="A3:D3 A71:D145 D4 A4:A5 B5:C5">
-    <cfRule type="cellIs" dxfId="51" priority="7" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="6" priority="7" stopIfTrue="1" operator="lessThan">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A6:D67">
-    <cfRule type="cellIs" dxfId="50" priority="4" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="5" priority="4" stopIfTrue="1" operator="lessThan">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A68:D70">
-    <cfRule type="cellIs" dxfId="49" priority="1" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="4" priority="1" stopIfTrue="1" operator="lessThan">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A159:D163">
-    <cfRule type="cellIs" dxfId="48" priority="6" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="3" priority="6" stopIfTrue="1" operator="lessThan">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A170:D172">
-    <cfRule type="cellIs" dxfId="47" priority="5" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="2" priority="5" stopIfTrue="1" operator="lessThan">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D1:D3 D71:D1048576 D6:D67">
-    <cfRule type="duplicateValues" dxfId="46" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D6:D66">
-    <cfRule type="duplicateValues" dxfId="45" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -40815,7 +40818,7 @@
       <c r="M4" s="370"/>
       <c r="N4" s="400">
         <f ca="1">'1'!N4:P4</f>
-        <v>46266</v>
+        <v>46269</v>
       </c>
       <c r="O4" s="400"/>
       <c r="P4" s="400"/>
@@ -40843,7 +40846,7 @@
       <c r="M5" s="370"/>
       <c r="N5" s="400">
         <f ca="1">N4-1</f>
-        <v>46265</v>
+        <v>46268</v>
       </c>
       <c r="O5" s="369"/>
       <c r="P5" s="369"/>
@@ -40865,7 +40868,7 @@
       <c r="M6" s="370"/>
       <c r="N6" s="399" t="str">
         <f>Summary!H2</f>
-        <v>Booker Name</v>
+        <v>Jabbar</v>
       </c>
       <c r="O6" s="399"/>
       <c r="P6" s="399"/>
@@ -42239,7 +42242,7 @@
       <c r="M4" s="370"/>
       <c r="N4" s="400">
         <f ca="1">'1'!N4:P4</f>
-        <v>46266</v>
+        <v>46269</v>
       </c>
       <c r="O4" s="400"/>
       <c r="P4" s="400"/>
@@ -42267,7 +42270,7 @@
       <c r="M5" s="370"/>
       <c r="N5" s="400">
         <f ca="1">N4-1</f>
-        <v>46265</v>
+        <v>46268</v>
       </c>
       <c r="O5" s="369"/>
       <c r="P5" s="369"/>
@@ -42289,7 +42292,7 @@
       <c r="M6" s="370"/>
       <c r="N6" s="399" t="str">
         <f>Summary!H2</f>
-        <v>Booker Name</v>
+        <v>Jabbar</v>
       </c>
       <c r="O6" s="399"/>
       <c r="P6" s="399"/>
@@ -43663,7 +43666,7 @@
       <c r="M4" s="370"/>
       <c r="N4" s="400">
         <f ca="1">'1'!N4:P4</f>
-        <v>46266</v>
+        <v>46269</v>
       </c>
       <c r="O4" s="400"/>
       <c r="P4" s="400"/>
@@ -43691,7 +43694,7 @@
       <c r="M5" s="370"/>
       <c r="N5" s="400">
         <f ca="1">N4-1</f>
-        <v>46265</v>
+        <v>46268</v>
       </c>
       <c r="O5" s="369"/>
       <c r="P5" s="369"/>
@@ -43713,7 +43716,7 @@
       <c r="M6" s="370"/>
       <c r="N6" s="399" t="str">
         <f>Summary!H2</f>
-        <v>Booker Name</v>
+        <v>Jabbar</v>
       </c>
       <c r="O6" s="399"/>
       <c r="P6" s="399"/>
@@ -45087,7 +45090,7 @@
       <c r="M4" s="370"/>
       <c r="N4" s="400">
         <f ca="1">'1'!N4:P4</f>
-        <v>46266</v>
+        <v>46269</v>
       </c>
       <c r="O4" s="400"/>
       <c r="P4" s="400"/>
@@ -45115,7 +45118,7 @@
       <c r="M5" s="370"/>
       <c r="N5" s="400">
         <f ca="1">N4-1</f>
-        <v>46265</v>
+        <v>46268</v>
       </c>
       <c r="O5" s="369"/>
       <c r="P5" s="369"/>
@@ -45137,7 +45140,7 @@
       <c r="M6" s="370"/>
       <c r="N6" s="399" t="str">
         <f>Summary!H2</f>
-        <v>Booker Name</v>
+        <v>Jabbar</v>
       </c>
       <c r="O6" s="399"/>
       <c r="P6" s="399"/>
@@ -46511,7 +46514,7 @@
       <c r="M4" s="370"/>
       <c r="N4" s="400">
         <f ca="1">'1'!N4:P4</f>
-        <v>46266</v>
+        <v>46269</v>
       </c>
       <c r="O4" s="400"/>
       <c r="P4" s="400"/>
@@ -46539,7 +46542,7 @@
       <c r="M5" s="370"/>
       <c r="N5" s="400">
         <f ca="1">N4-1</f>
-        <v>46265</v>
+        <v>46268</v>
       </c>
       <c r="O5" s="369"/>
       <c r="P5" s="369"/>
@@ -46561,7 +46564,7 @@
       <c r="M6" s="370"/>
       <c r="N6" s="399" t="str">
         <f>Summary!H2</f>
-        <v>Booker Name</v>
+        <v>Jabbar</v>
       </c>
       <c r="O6" s="399"/>
       <c r="P6" s="399"/>
@@ -47929,7 +47932,7 @@
       <c r="L4" s="370"/>
       <c r="M4" s="400">
         <f ca="1">TODAY()+1</f>
-        <v>46267</v>
+        <v>46270</v>
       </c>
       <c r="N4" s="400"/>
       <c r="O4" s="400"/>
@@ -47957,7 +47960,7 @@
       <c r="L5" s="370"/>
       <c r="M5" s="400">
         <f ca="1">M4-1</f>
-        <v>46266</v>
+        <v>46269</v>
       </c>
       <c r="N5" s="369"/>
       <c r="O5" s="369"/>
@@ -50605,47 +50608,47 @@
     <mergeCell ref="T20:T21"/>
   </mergeCells>
   <conditionalFormatting sqref="C1 C3:C5">
-    <cfRule type="cellIs" dxfId="44" priority="1" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="51" priority="1" stopIfTrue="1" operator="lessThan">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C3:C5">
-    <cfRule type="duplicateValues" dxfId="43" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C7 C9:C11 C15:C17 C22:C25">
-    <cfRule type="cellIs" dxfId="42" priority="22" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="49" priority="22" stopIfTrue="1" operator="lessThan">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C9:C11">
-    <cfRule type="duplicateValues" dxfId="41" priority="52"/>
+    <cfRule type="duplicateValues" dxfId="48" priority="52"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C13">
-    <cfRule type="cellIs" dxfId="40" priority="18" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="47" priority="18" stopIfTrue="1" operator="lessThan">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C15:C17">
-    <cfRule type="duplicateValues" dxfId="39" priority="58"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="58"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C20">
-    <cfRule type="cellIs" dxfId="38" priority="14" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="45" priority="14" stopIfTrue="1" operator="lessThan">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C22:C25">
-    <cfRule type="duplicateValues" dxfId="37" priority="45"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="45"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C27">
-    <cfRule type="cellIs" dxfId="36" priority="10" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="43" priority="10" stopIfTrue="1" operator="lessThan">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C29:C31">
-    <cfRule type="cellIs" dxfId="35" priority="3" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="42" priority="3" stopIfTrue="1" operator="lessThan">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="duplicateValues" dxfId="34" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="4"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -50908,12 +50911,12 @@
   </mergeCells>
   <phoneticPr fontId="23" type="noConversion"/>
   <conditionalFormatting sqref="B1 B3:B5">
-    <cfRule type="cellIs" dxfId="33" priority="1" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="40" priority="1" stopIfTrue="1" operator="lessThan">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:B5">
-    <cfRule type="duplicateValues" dxfId="32" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="2"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -54009,82 +54012,82 @@
     <mergeCell ref="F215:F220"/>
   </mergeCells>
   <conditionalFormatting sqref="G5:G12 G14:G16 G35:G41 G44:G58">
-    <cfRule type="duplicateValues" dxfId="31" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="30"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G35:G41 G44:G52">
-    <cfRule type="duplicateValues" dxfId="30" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="32"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G42">
-    <cfRule type="duplicateValues" dxfId="29" priority="24"/>
-    <cfRule type="duplicateValues" dxfId="28" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="25"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G43">
-    <cfRule type="duplicateValues" dxfId="27" priority="28"/>
-    <cfRule type="duplicateValues" dxfId="26" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="29"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G44">
-    <cfRule type="duplicateValues" dxfId="25" priority="26"/>
-    <cfRule type="duplicateValues" dxfId="24" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="27"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G46">
-    <cfRule type="duplicateValues" dxfId="23" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="31"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G65:G102 G104:G118">
-    <cfRule type="duplicateValues" dxfId="22" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="21"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G95:G102 G104:G112">
-    <cfRule type="duplicateValues" dxfId="21" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="23"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G103">
-    <cfRule type="duplicateValues" dxfId="20" priority="19"/>
-    <cfRule type="duplicateValues" dxfId="19" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G104">
-    <cfRule type="duplicateValues" dxfId="18" priority="17"/>
-    <cfRule type="duplicateValues" dxfId="17" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="18"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G106">
-    <cfRule type="duplicateValues" dxfId="16" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="22"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G125:G162 G164:G178">
-    <cfRule type="duplicateValues" dxfId="15" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G155:G162 G164:G172">
-    <cfRule type="duplicateValues" dxfId="14" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G163">
-    <cfRule type="duplicateValues" dxfId="13" priority="12"/>
-    <cfRule type="duplicateValues" dxfId="12" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G164">
-    <cfRule type="duplicateValues" dxfId="11" priority="10"/>
-    <cfRule type="duplicateValues" dxfId="10" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G166">
-    <cfRule type="duplicateValues" dxfId="9" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G203">
-    <cfRule type="duplicateValues" dxfId="8" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G204">
-    <cfRule type="duplicateValues" dxfId="7" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G215:G222 G225:G232">
-    <cfRule type="duplicateValues" dxfId="6" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G223">
-    <cfRule type="duplicateValues" dxfId="5" priority="5"/>
-    <cfRule type="duplicateValues" dxfId="4" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G224">
-    <cfRule type="duplicateValues" dxfId="3" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G225:G232 G185:G202 G205:G222 G236:G238">
-    <cfRule type="duplicateValues" dxfId="1" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G226">
-    <cfRule type="duplicateValues" dxfId="0" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="8"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -54129,7 +54132,7 @@
       <c r="F2" s="356"/>
       <c r="G2" s="356"/>
       <c r="H2" s="353" t="s">
-        <v>498</v>
+        <v>514</v>
       </c>
       <c r="I2" s="353"/>
       <c r="J2" s="354"/>
@@ -54152,7 +54155,7 @@
       <c r="G3" s="360"/>
       <c r="H3" s="357">
         <f ca="1">TODAY()</f>
-        <v>46266</v>
+        <v>46269</v>
       </c>
       <c r="I3" s="357"/>
       <c r="J3" s="358"/>
@@ -55672,7 +55675,7 @@
       <c r="M4" s="370"/>
       <c r="N4" s="400">
         <f ca="1">Summary!H3</f>
-        <v>46266</v>
+        <v>46269</v>
       </c>
       <c r="O4" s="400"/>
       <c r="P4" s="400"/>
@@ -55700,7 +55703,7 @@
       <c r="M5" s="370"/>
       <c r="N5" s="400">
         <f ca="1">N4-1</f>
-        <v>46265</v>
+        <v>46268</v>
       </c>
       <c r="O5" s="369"/>
       <c r="P5" s="369"/>
@@ -55722,7 +55725,7 @@
       <c r="M6" s="370"/>
       <c r="N6" s="399" t="str">
         <f>Summary!H2</f>
-        <v>Booker Name</v>
+        <v>Jabbar</v>
       </c>
       <c r="O6" s="399"/>
       <c r="P6" s="399"/>
@@ -57085,7 +57088,7 @@
       <c r="M4" s="370"/>
       <c r="N4" s="400">
         <f ca="1">'1'!N4:P4</f>
-        <v>46266</v>
+        <v>46269</v>
       </c>
       <c r="O4" s="400"/>
       <c r="P4" s="400"/>
@@ -57113,7 +57116,7 @@
       <c r="M5" s="370"/>
       <c r="N5" s="400">
         <f ca="1">N4-1</f>
-        <v>46265</v>
+        <v>46268</v>
       </c>
       <c r="O5" s="369"/>
       <c r="P5" s="369"/>
@@ -57135,7 +57138,7 @@
       <c r="M6" s="370"/>
       <c r="N6" s="399" t="str">
         <f>Summary!H2</f>
-        <v>Booker Name</v>
+        <v>Jabbar</v>
       </c>
       <c r="O6" s="399"/>
       <c r="P6" s="399"/>
@@ -58509,7 +58512,7 @@
       <c r="M4" s="370"/>
       <c r="N4" s="400">
         <f ca="1">'1'!N4:P4</f>
-        <v>46266</v>
+        <v>46269</v>
       </c>
       <c r="O4" s="400"/>
       <c r="P4" s="400"/>
@@ -58537,7 +58540,7 @@
       <c r="M5" s="370"/>
       <c r="N5" s="400">
         <f ca="1">N4-1</f>
-        <v>46265</v>
+        <v>46268</v>
       </c>
       <c r="O5" s="369"/>
       <c r="P5" s="369"/>
@@ -58559,7 +58562,7 @@
       <c r="M6" s="370"/>
       <c r="N6" s="399" t="str">
         <f>Summary!H2</f>
-        <v>Booker Name</v>
+        <v>Jabbar</v>
       </c>
       <c r="O6" s="399"/>
       <c r="P6" s="399"/>
@@ -59933,7 +59936,7 @@
       <c r="M4" s="370"/>
       <c r="N4" s="400">
         <f ca="1">'1'!N4:P4</f>
-        <v>46266</v>
+        <v>46269</v>
       </c>
       <c r="O4" s="400"/>
       <c r="P4" s="400"/>
@@ -59961,7 +59964,7 @@
       <c r="M5" s="370"/>
       <c r="N5" s="400">
         <f ca="1">N4-1</f>
-        <v>46265</v>
+        <v>46268</v>
       </c>
       <c r="O5" s="369"/>
       <c r="P5" s="369"/>
@@ -59983,7 +59986,7 @@
       <c r="M6" s="370"/>
       <c r="N6" s="399" t="str">
         <f>Summary!H2</f>
-        <v>Booker Name</v>
+        <v>Jabbar</v>
       </c>
       <c r="O6" s="399"/>
       <c r="P6" s="399"/>
@@ -61357,7 +61360,7 @@
       <c r="M4" s="370"/>
       <c r="N4" s="400">
         <f ca="1">'1'!N4:P4</f>
-        <v>46266</v>
+        <v>46269</v>
       </c>
       <c r="O4" s="400"/>
       <c r="P4" s="400"/>
@@ -61385,7 +61388,7 @@
       <c r="M5" s="370"/>
       <c r="N5" s="400">
         <f ca="1">N4-1</f>
-        <v>46265</v>
+        <v>46268</v>
       </c>
       <c r="O5" s="369"/>
       <c r="P5" s="369"/>
@@ -61407,7 +61410,7 @@
       <c r="M6" s="370"/>
       <c r="N6" s="399" t="str">
         <f>Summary!H2</f>
-        <v>Booker Name</v>
+        <v>Jabbar</v>
       </c>
       <c r="O6" s="399"/>
       <c r="P6" s="399"/>
